--- a/ExcelFiles/TutorialsNinja.xlsx
+++ b/ExcelFiles/TutorialsNinja.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arunm\PycharmProjects\SeleniumPythonHybridFramework\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\QAFox\localrepos\PythonRepos\SeleniumPythonHybridPageObjectModelFramework\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C91AE0-7B0E-459F-8E79-B10C11FF49F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A30FAA-32C6-4109-9347-B1A14C3D0612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LoginTest" sheetId="1" r:id="rId1"/>
-    <sheet name="RegisterTest" sheetId="2" r:id="rId2"/>
+    <sheet name="TestLoginData" sheetId="3" r:id="rId1"/>
+    <sheet name="LoginTest" sheetId="1" r:id="rId2"/>
+    <sheet name="RegisterTest" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Username</t>
   </si>
@@ -62,6 +63,18 @@
   </si>
   <si>
     <t>Motoori</t>
+  </si>
+  <si>
+    <t>ValidEmail</t>
+  </si>
+  <si>
+    <t>ValidPassword</t>
+  </si>
+  <si>
+    <t>InvalidPassword</t>
+  </si>
+  <si>
+    <t>amotooricap8@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -127,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -136,6 +149,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -418,15 +437,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27316617-4937-4795-AA58-B977DA94E125}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="7">
+        <v>12345</v>
+      </c>
+      <c r="C2" s="7">
+        <v>67890</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{F46D3EEF-533A-4200-9865-978FA82238C1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -434,7 +493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -442,7 +501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -450,7 +509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -468,12 +527,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881A56EE-EDE1-4CA9-B455-9AAE669FBC69}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
@@ -481,7 +540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
